--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.16971177731578</v>
+        <v>6.690078163813814</v>
       </c>
       <c r="D2" t="n">
-        <v>41.34429140231489</v>
+        <v>6.718447352876169</v>
       </c>
       <c r="E2" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F2" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.39860346077858</v>
+        <v>5.26477306237652</v>
       </c>
       <c r="D3" t="n">
-        <v>32.70009321545449</v>
+        <v>5.313765147511355</v>
       </c>
       <c r="E3" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F3" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.15493930020081</v>
+        <v>5.387677636282632</v>
       </c>
       <c r="D4" t="n">
-        <v>55.12785621309057</v>
+        <v>8.958276634627218</v>
       </c>
       <c r="E4" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F4" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.38056075669969</v>
+        <v>5.9118411229637</v>
       </c>
       <c r="D5" t="n">
-        <v>35.77588921803309</v>
+        <v>5.813581997930377</v>
       </c>
       <c r="E5" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F5" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.81955973367425</v>
+        <v>5.333178456722066</v>
       </c>
       <c r="D6" t="n">
-        <v>32.44790179435294</v>
+        <v>5.272784041582353</v>
       </c>
       <c r="E6" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F6" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.76825027991175</v>
+        <v>4.18734067048566</v>
       </c>
       <c r="D7" t="n">
-        <v>47.42191882637135</v>
+        <v>7.706061809285344</v>
       </c>
       <c r="E7" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F7" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>10.48977882331825</v>
+        <v>1.704589058789216</v>
       </c>
       <c r="D8" t="n">
-        <v>31.92326293936791</v>
+        <v>5.187530227647285</v>
       </c>
       <c r="E8" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F8" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.15406271587613</v>
+        <v>5.550035191329871</v>
       </c>
       <c r="D9" t="n">
-        <v>39.26918048780309</v>
+        <v>6.381241829268003</v>
       </c>
       <c r="E9" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F9" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>41.3061051507641</v>
+        <v>6.712242086999167</v>
       </c>
       <c r="D10" t="n">
-        <v>40.95420847271959</v>
+        <v>6.655058876816933</v>
       </c>
       <c r="E10" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F10" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.23352587874544</v>
+        <v>5.075447955296133</v>
       </c>
       <c r="D11" t="n">
-        <v>30.04275204106197</v>
+        <v>4.88194720667257</v>
       </c>
       <c r="E11" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F11" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>6.670832032063167</v>
+        <v>1.084010205210265</v>
       </c>
       <c r="D12" t="n">
-        <v>32.92647350378987</v>
+        <v>5.350551944365854</v>
       </c>
       <c r="E12" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F12" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>7.3824115301167</v>
+        <v>1.199641873643964</v>
       </c>
       <c r="D13" t="n">
-        <v>25.24220094337391</v>
+        <v>4.101857653298261</v>
       </c>
       <c r="E13" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F13" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>7.778174593052023</v>
+        <v>1.263953371370954</v>
       </c>
       <c r="D14" t="n">
-        <v>27.58489578696273</v>
+        <v>4.482545565381444</v>
       </c>
       <c r="E14" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F14" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>23.86603651140011</v>
+        <v>3.878230933102519</v>
       </c>
       <c r="D15" t="n">
-        <v>23.49644956678053</v>
+        <v>3.818173054601836</v>
       </c>
       <c r="E15" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F15" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>14.86999041607836</v>
+        <v>2.416373442612734</v>
       </c>
       <c r="D16" t="n">
-        <v>15.12928656030326</v>
+        <v>2.458509066049279</v>
       </c>
       <c r="E16" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F16" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>22.21565917391954</v>
+        <v>3.610044615761926</v>
       </c>
       <c r="D17" t="n">
-        <v>21.23588871243766</v>
+        <v>3.450831915771119</v>
       </c>
       <c r="E17" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F17" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>28.32079302597498</v>
+        <v>4.602128866720935</v>
       </c>
       <c r="D18" t="n">
-        <v>24.17683577919903</v>
+        <v>3.928735814119843</v>
       </c>
       <c r="E18" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F18" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31.82742916690643</v>
+        <v>5.171957239622294</v>
       </c>
       <c r="D19" t="n">
-        <v>15.67464335940198</v>
+        <v>2.547129545902821</v>
       </c>
       <c r="E19" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F19" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>40.68391425168237</v>
+        <v>6.611136065898385</v>
       </c>
       <c r="D20" t="n">
-        <v>6.418992248604679</v>
+        <v>1.04308624039826</v>
       </c>
       <c r="E20" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F20" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>36.12574323960715</v>
+        <v>5.870433276436161</v>
       </c>
       <c r="D21" t="n">
-        <v>35.8523720120768</v>
+        <v>5.82601045196248</v>
       </c>
       <c r="E21" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F21" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>11.652310619747</v>
+        <v>1.893500475708887</v>
       </c>
       <c r="D22" t="n">
-        <v>12.39690952760825</v>
+        <v>2.014497798236341</v>
       </c>
       <c r="E22" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F22" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>32.02119902984859</v>
+        <v>5.203444842350396</v>
       </c>
       <c r="D23" t="n">
-        <v>32.18105744097149</v>
+        <v>5.229421834157868</v>
       </c>
       <c r="E23" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F23" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>36.89429229698115</v>
+        <v>5.995322498259437</v>
       </c>
       <c r="D24" t="n">
-        <v>37.6101758047266</v>
+        <v>6.111653568268073</v>
       </c>
       <c r="E24" t="n">
-        <v>11.30427164763959</v>
+        <v>1.836944142741434</v>
       </c>
       <c r="F24" t="n">
-        <v>11.22313097196474</v>
+        <v>1.82375878294427</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
